--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/observations-summary.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
   <si>
     <t>Profile</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>JP Core Observation Radiology Findings Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#imaging</t>
   </si>
   <si>
     <t>null#18782-3</t>
@@ -725,13 +728,13 @@
         <v>59</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>23</v>
@@ -740,7 +743,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -754,19 +757,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>23</v>
@@ -775,7 +778,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -789,13 +792,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>14</v>
@@ -804,7 +807,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>16</v>
@@ -824,13 +827,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>14</v>
@@ -839,7 +842,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>16</v>
